--- a/samples/outputs/XQ-4108785_parsed.xlsx
+++ b/samples/outputs/XQ-4108785_parsed.xlsx
@@ -678,10 +678,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V4" s="0">
         <x:v>1</x:v>
@@ -710,10 +710,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T5" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U5" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V5" s="0">
         <x:v>1</x:v>
@@ -742,10 +742,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T6" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U6" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V6" s="0">
         <x:v>1</x:v>
@@ -774,10 +774,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T7" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U7" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V7" s="0">
         <x:v>1</x:v>
@@ -806,10 +806,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T8" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U8" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V8" s="0">
         <x:v>1</x:v>
@@ -838,10 +838,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T9" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U9" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V9" s="0">
         <x:v>1</x:v>
@@ -908,10 +908,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T11" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U11" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V11" s="0">
         <x:v>1</x:v>
@@ -972,7 +972,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T13" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U13" s="0">
         <x:v>4003.51</x:v>
